--- a/data/exchange_rates/USD_CZK.xlsx
+++ b/data/exchange_rates/USD_CZK.xlsx
@@ -429,21 +429,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CZK= (BID)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
@@ -451,477 +456,511 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>45292</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.324</v>
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>44928</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08822476735862568</v>
+        <v>22.352</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.008956282699299378</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>44928</v>
-      </c>
-      <c r="C3" t="n">
-        <v>22.352</v>
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>44564</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.008956282699299378</v>
+        <v>22.554</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.03226692297130296</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="C4" t="n">
-        <v>22.554</v>
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>44197</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03226692297130296</v>
+        <v>21.849</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.01874388026297389</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>44197</v>
-      </c>
-      <c r="C5" t="n">
-        <v>21.849</v>
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>43831</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01874388026297389</v>
+        <v>21.447</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.05361397934868943</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C6" t="n">
-        <v>21.447</v>
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>43466</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.05361397934868943</v>
+        <v>22.662</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01101940664733437</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>43466</v>
-      </c>
-      <c r="C7" t="n">
-        <v>22.662</v>
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>43101</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01101940664733437</v>
+        <v>22.415</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05343547325876494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>43101</v>
-      </c>
-      <c r="C8" t="n">
-        <v>22.415</v>
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>42737</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05343547325876494</v>
+        <v>21.278</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.1703836556456644</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>42737</v>
-      </c>
-      <c r="C9" t="n">
-        <v>21.278</v>
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>42370</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1703836556456644</v>
+        <v>25.648</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03165600740115036</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>42370</v>
-      </c>
-      <c r="C10" t="n">
-        <v>25.648</v>
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>42005</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03165600740115036</v>
+        <v>24.861</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.08886650315346881</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>42005</v>
-      </c>
-      <c r="C11" t="n">
-        <v>24.861</v>
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>41640</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08886650315346881</v>
+        <v>22.832</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1493003120910098</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>41640</v>
-      </c>
-      <c r="C12" t="n">
-        <v>22.832</v>
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>41275</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1493003120910098</v>
+        <v>19.866</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.04640505662365026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>41275</v>
-      </c>
-      <c r="C13" t="n">
-        <v>19.866</v>
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>40910</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04640505662365026</v>
+        <v>18.985</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.03785728765457125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>40910</v>
-      </c>
-      <c r="C14" t="n">
-        <v>18.985</v>
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>40546</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.03785728765457125</v>
+        <v>19.732</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.05699592886222413</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>40546</v>
-      </c>
-      <c r="C15" t="n">
-        <v>19.732</v>
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>40179</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05699592886222413</v>
+        <v>18.668</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01583501115524843</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>40179</v>
-      </c>
-      <c r="C16" t="n">
-        <v>18.668</v>
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>39814</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01583501115524843</v>
+        <v>18.377</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.03855812493460301</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>39814</v>
-      </c>
-      <c r="C17" t="n">
-        <v>18.377</v>
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>39448</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.03855812493460301</v>
+        <v>19.114</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.05206957287538538</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>39448</v>
-      </c>
-      <c r="C18" t="n">
-        <v>19.114</v>
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>19</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>39083</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05206957287538538</v>
+        <v>18.168</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.1273775216138329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>39083</v>
-      </c>
-      <c r="C19" t="n">
-        <v>18.168</v>
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>38719</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1273775216138329</v>
+        <v>20.82</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.1513817559305453</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>38719</v>
-      </c>
-      <c r="C20" t="n">
-        <v>20.82</v>
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>21</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>38355</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1513817559305453</v>
+        <v>24.534</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.09453490965871068</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>38355</v>
-      </c>
-      <c r="C21" t="n">
-        <v>24.534</v>
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>22</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>37987</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09453490965871068</v>
+        <v>22.415</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.1268697413524463</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>37987</v>
-      </c>
-      <c r="C22" t="n">
-        <v>22.415</v>
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>37622</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1268697413524463</v>
+        <v>25.672</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.1454345727505742</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>37622</v>
-      </c>
-      <c r="C23" t="n">
-        <v>25.672</v>
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>24</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>37258</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1454345727505742</v>
+        <v>30.041</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.1556298836359549</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>37258</v>
-      </c>
-      <c r="C24" t="n">
-        <v>30.041</v>
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>25</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>36893</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1556298836359549</v>
+        <v>35.578</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.05382692409978176</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>36893</v>
-      </c>
-      <c r="C25" t="n">
-        <v>35.578</v>
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>36528</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.05382692409978176</v>
+        <v>37.602</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.05062866722548191</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>36528</v>
-      </c>
-      <c r="C26" t="n">
-        <v>37.602</v>
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>27</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>36164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.05062866722548191</v>
+        <v>35.79</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1947124211369629</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>36164</v>
-      </c>
-      <c r="C27" t="n">
-        <v>35.79</v>
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>28</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>35797</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1947124211369629</v>
+        <v>29.957</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.1356147387252213</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>35797</v>
-      </c>
-      <c r="C28" t="n">
-        <v>29.957</v>
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>35432</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1356147387252213</v>
+        <v>34.657</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2735457318193509</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>35432</v>
-      </c>
-      <c r="C29" t="n">
-        <v>34.657</v>
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>35066</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2735457318193509</v>
+        <v>27.213</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.02070439968493303</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>35066</v>
-      </c>
-      <c r="C30" t="n">
-        <v>27.213</v>
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>31</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>34701</v>
       </c>
       <c r="D30" t="n">
-        <v>0.02070439968493303</v>
+        <v>26.661</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.04543501611170778</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>34701</v>
-      </c>
-      <c r="C31" t="n">
-        <v>26.661</v>
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>32</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>34337</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.04543501611170778</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>34337</v>
-      </c>
-      <c r="C32" t="n">
         <v>27.93</v>
       </c>
-      <c r="D32" t="n">
-        <v>-0.06931022992335893</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>33970</v>
-      </c>
-      <c r="C33" t="n">
-        <v>30.01</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.03844423682480365</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>33604</v>
-      </c>
-      <c r="C34" t="n">
-        <v>28.899</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.03803879310344831</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>33239</v>
-      </c>
-      <c r="C35" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/exchange_rates/USD_CZK.xlsx
+++ b/data/exchange_rates/USD_CZK.xlsx
@@ -429,26 +429,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>CZK= (BID)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
@@ -456,511 +451,449 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>44928</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.352</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.008956282699299378</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>34337</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>44564</v>
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>34701</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26.661</v>
       </c>
       <c r="D3" t="n">
-        <v>22.554</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.03226692297130296</v>
+        <v>-0.0454</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>44197</v>
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>35066</v>
+      </c>
+      <c r="C4" t="n">
+        <v>27.213</v>
       </c>
       <c r="D4" t="n">
-        <v>21.849</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.01874388026297389</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>43831</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>35432</v>
+      </c>
+      <c r="C5" t="n">
+        <v>34.657</v>
       </c>
       <c r="D5" t="n">
-        <v>21.447</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.05361397934868943</v>
+        <v>0.2735</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>43466</v>
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>35797</v>
+      </c>
+      <c r="C6" t="n">
+        <v>29.957</v>
       </c>
       <c r="D6" t="n">
-        <v>22.662</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.01101940664733437</v>
+        <v>-0.1356</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>43101</v>
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>36164</v>
+      </c>
+      <c r="C7" t="n">
+        <v>35.79</v>
       </c>
       <c r="D7" t="n">
-        <v>22.415</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.05343547325876494</v>
+        <v>0.1947</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>42737</v>
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>36528</v>
+      </c>
+      <c r="C8" t="n">
+        <v>37.602</v>
       </c>
       <c r="D8" t="n">
-        <v>21.278</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.1703836556456644</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>42370</v>
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>36893</v>
+      </c>
+      <c r="C9" t="n">
+        <v>35.578</v>
       </c>
       <c r="D9" t="n">
-        <v>25.648</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.03165600740115036</v>
+        <v>-0.0538</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>11</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>42005</v>
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>37258</v>
+      </c>
+      <c r="C10" t="n">
+        <v>30.041</v>
       </c>
       <c r="D10" t="n">
-        <v>24.861</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.08886650315346881</v>
+        <v>-0.1556</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>41640</v>
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>37622</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25.672</v>
       </c>
       <c r="D11" t="n">
-        <v>22.832</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.1493003120910098</v>
+        <v>-0.1454</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>41275</v>
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>37987</v>
+      </c>
+      <c r="C12" t="n">
+        <v>22.415</v>
       </c>
       <c r="D12" t="n">
-        <v>19.866</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.04640505662365026</v>
+        <v>-0.1269</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>40910</v>
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>38355</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24.534</v>
       </c>
       <c r="D13" t="n">
-        <v>18.985</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.03785728765457125</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>40546</v>
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>38719</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20.82</v>
       </c>
       <c r="D14" t="n">
-        <v>19.732</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.05699592886222413</v>
+        <v>-0.1514</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>40179</v>
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>39083</v>
+      </c>
+      <c r="C15" t="n">
+        <v>18.168</v>
       </c>
       <c r="D15" t="n">
-        <v>18.668</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.01583501115524843</v>
+        <v>-0.1274</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>17</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>39814</v>
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>39448</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19.114</v>
       </c>
       <c r="D16" t="n">
-        <v>18.377</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0.03855812493460301</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>18</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>39448</v>
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>39814</v>
+      </c>
+      <c r="C17" t="n">
+        <v>18.377</v>
       </c>
       <c r="D17" t="n">
-        <v>19.114</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.05206957287538538</v>
+        <v>-0.0386</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>19</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>39083</v>
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>40179</v>
+      </c>
+      <c r="C18" t="n">
+        <v>18.668</v>
       </c>
       <c r="D18" t="n">
-        <v>18.168</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.1273775216138329</v>
+        <v>0.0158</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>20</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>38719</v>
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>40546</v>
+      </c>
+      <c r="C19" t="n">
+        <v>19.732</v>
       </c>
       <c r="D19" t="n">
-        <v>20.82</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0.1513817559305453</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>21</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>38355</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>40910</v>
+      </c>
+      <c r="C20" t="n">
+        <v>18.985</v>
       </c>
       <c r="D20" t="n">
-        <v>24.534</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.09453490965871068</v>
+        <v>-0.0379</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>22</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>37987</v>
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>41275</v>
+      </c>
+      <c r="C21" t="n">
+        <v>19.866</v>
       </c>
       <c r="D21" t="n">
-        <v>22.415</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.1268697413524463</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="n">
-        <v>23</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>37622</v>
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>41640</v>
+      </c>
+      <c r="C22" t="n">
+        <v>22.832</v>
       </c>
       <c r="D22" t="n">
-        <v>25.672</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-0.1454345727505742</v>
+        <v>0.1493</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="n">
-        <v>24</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>37258</v>
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>42005</v>
+      </c>
+      <c r="C23" t="n">
+        <v>24.861</v>
       </c>
       <c r="D23" t="n">
-        <v>30.041</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-0.1556298836359549</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="n">
-        <v>25</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>36893</v>
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>42370</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25.648</v>
       </c>
       <c r="D24" t="n">
-        <v>35.578</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.05382692409978176</v>
+        <v>0.0317</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="n">
-        <v>26</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>36528</v>
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>42737</v>
+      </c>
+      <c r="C25" t="n">
+        <v>21.278</v>
       </c>
       <c r="D25" t="n">
-        <v>37.602</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.05062866722548191</v>
+        <v>-0.1704</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="n">
-        <v>27</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>36164</v>
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>43101</v>
+      </c>
+      <c r="C26" t="n">
+        <v>22.415</v>
       </c>
       <c r="D26" t="n">
-        <v>35.79</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.1947124211369629</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="n">
-        <v>28</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>35797</v>
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C27" t="n">
+        <v>22.662</v>
       </c>
       <c r="D27" t="n">
-        <v>29.957</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-0.1356147387252213</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="n">
-        <v>29</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>35432</v>
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C28" t="n">
+        <v>21.447</v>
       </c>
       <c r="D28" t="n">
-        <v>34.657</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.2735457318193509</v>
+        <v>-0.0536</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="n">
-        <v>30</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>35066</v>
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C29" t="n">
+        <v>21.849</v>
       </c>
       <c r="D29" t="n">
-        <v>27.213</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.02070439968493303</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="n">
-        <v>31</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>34701</v>
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="C30" t="n">
+        <v>22.554</v>
       </c>
       <c r="D30" t="n">
-        <v>26.661</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0.04543501611170778</v>
+        <v>0.0323</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>44928</v>
+      </c>
+      <c r="C31" t="n">
+        <v>22.352</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
-        <v>32</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>34337</v>
-      </c>
-      <c r="D31" t="n">
-        <v>27.93</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="B32" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C32" t="n">
+        <v>24.324</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0882</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C33" t="n">
+        <v>23.975</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.0143</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/exchange_rates/USD_CZK.xlsx
+++ b/data/exchange_rates/USD_CZK.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,11 @@
           <t>Returns</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Z-Score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -460,6 +465,7 @@
         <v>27.93</v>
       </c>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -474,6 +480,9 @@
       <c r="D3" t="n">
         <v>-0.0454</v>
       </c>
+      <c r="E3" t="n">
+        <v>-0.4406537068705871</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -488,6 +497,9 @@
       <c r="D4" t="n">
         <v>0.0207</v>
       </c>
+      <c r="E4" t="n">
+        <v>0.1948192403801133</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -502,6 +514,9 @@
       <c r="D5" t="n">
         <v>0.2735</v>
       </c>
+      <c r="E5" t="n">
+        <v>2.625190814736801</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -516,6 +531,9 @@
       <c r="D6" t="n">
         <v>-0.1356</v>
       </c>
+      <c r="E6" t="n">
+        <v>-1.307819513860196</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -530,6 +548,9 @@
       <c r="D7" t="n">
         <v>0.1947</v>
       </c>
+      <c r="E7" t="n">
+        <v>1.867622460071821</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -544,6 +565,9 @@
       <c r="D8" t="n">
         <v>0.0506</v>
       </c>
+      <c r="E8" t="n">
+        <v>0.4822722074420791</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -558,6 +582,9 @@
       <c r="D9" t="n">
         <v>-0.0538</v>
       </c>
+      <c r="E9" t="n">
+        <v>-0.5214097243729454</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -572,6 +599,9 @@
       <c r="D10" t="n">
         <v>-0.1556</v>
       </c>
+      <c r="E10" t="n">
+        <v>-1.500095746008668</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -586,6 +616,9 @@
       <c r="D11" t="n">
         <v>-0.1454</v>
       </c>
+      <c r="E11" t="n">
+        <v>-1.402034867612948</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -600,6 +633,9 @@
       <c r="D12" t="n">
         <v>-0.1269</v>
       </c>
+      <c r="E12" t="n">
+        <v>-1.224179352875611</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -614,6 +650,9 @@
       <c r="D13" t="n">
         <v>0.0945</v>
       </c>
+      <c r="E13" t="n">
+        <v>0.9043185370079754</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -628,6 +667,9 @@
       <c r="D14" t="n">
         <v>-0.1514</v>
       </c>
+      <c r="E14" t="n">
+        <v>-1.459717737257489</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -642,6 +684,9 @@
       <c r="D15" t="n">
         <v>-0.1274</v>
       </c>
+      <c r="E15" t="n">
+        <v>-1.228986258679323</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -656,6 +701,9 @@
       <c r="D16" t="n">
         <v>0.0521</v>
       </c>
+      <c r="E16" t="n">
+        <v>0.4966929248532145</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -670,6 +718,9 @@
       <c r="D17" t="n">
         <v>-0.0386</v>
       </c>
+      <c r="E17" t="n">
+        <v>-0.3752797879401066</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -684,6 +735,9 @@
       <c r="D18" t="n">
         <v>0.0158</v>
       </c>
+      <c r="E18" t="n">
+        <v>0.1477115635037376</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -698,6 +752,9 @@
       <c r="D19" t="n">
         <v>0.057</v>
       </c>
+      <c r="E19" t="n">
+        <v>0.5438006017295902</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -712,6 +769,9 @@
       <c r="D20" t="n">
         <v>-0.0379</v>
       </c>
+      <c r="E20" t="n">
+        <v>-0.3685501198149101</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -726,6 +786,9 @@
       <c r="D21" t="n">
         <v>0.0464</v>
       </c>
+      <c r="E21" t="n">
+        <v>0.4418941986908999</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -740,6 +803,9 @@
       <c r="D22" t="n">
         <v>0.1493</v>
       </c>
+      <c r="E22" t="n">
+        <v>1.431155413094789</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -754,6 +820,9 @@
       <c r="D23" t="n">
         <v>0.08890000000000001</v>
       </c>
+      <c r="E23" t="n">
+        <v>0.8504811920064033</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -768,6 +837,9 @@
       <c r="D24" t="n">
         <v>0.0317</v>
       </c>
+      <c r="E24" t="n">
+        <v>0.3005711680617729</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -782,6 +854,9 @@
       <c r="D25" t="n">
         <v>-0.1704</v>
       </c>
+      <c r="E25" t="n">
+        <v>-1.642380157798538</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -796,6 +871,9 @@
       <c r="D26" t="n">
         <v>0.0534</v>
       </c>
+      <c r="E26" t="n">
+        <v>0.5091908799428653</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -810,6 +888,9 @@
       <c r="D27" t="n">
         <v>0.011</v>
       </c>
+      <c r="E27" t="n">
+        <v>0.1015652677881042</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -824,6 +905,9 @@
       <c r="D28" t="n">
         <v>-0.0536</v>
       </c>
+      <c r="E28" t="n">
+        <v>-0.5194869620514607</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -838,6 +922,9 @@
       <c r="D29" t="n">
         <v>0.0187</v>
       </c>
+      <c r="E29" t="n">
+        <v>0.175591617165266</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -852,6 +939,9 @@
       <c r="D30" t="n">
         <v>0.0323</v>
       </c>
+      <c r="E30" t="n">
+        <v>0.3063394550262271</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -866,6 +956,9 @@
       <c r="D31" t="n">
         <v>-0.008999999999999999</v>
       </c>
+      <c r="E31" t="n">
+        <v>-0.09071096436036787</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -880,6 +973,9 @@
       <c r="D32" t="n">
         <v>0.0882</v>
       </c>
+      <c r="E32" t="n">
+        <v>0.8437515238812067</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -893,6 +989,9 @@
       </c>
       <c r="D33" t="n">
         <v>-0.0143</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.141664165879713</v>
       </c>
     </row>
   </sheetData>

--- a/data/exchange_rates/USD_CZK.xlsx
+++ b/data/exchange_rates/USD_CZK.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,10 +445,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Z-Score</t>
         </is>
@@ -464,8 +469,11 @@
       <c r="C2" t="n">
         <v>27.93</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>1994</v>
+      </c>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -478,9 +486,12 @@
         <v>26.661</v>
       </c>
       <c r="D3" t="n">
+        <v>1995</v>
+      </c>
+      <c r="E3" t="n">
         <v>-0.0454</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>-0.4406537068705871</v>
       </c>
     </row>
@@ -495,9 +506,12 @@
         <v>27.213</v>
       </c>
       <c r="D4" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.0207</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.1948192403801133</v>
       </c>
     </row>
@@ -512,9 +526,12 @@
         <v>34.657</v>
       </c>
       <c r="D5" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.2735</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2.625190814736801</v>
       </c>
     </row>
@@ -529,9 +546,12 @@
         <v>29.957</v>
       </c>
       <c r="D6" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E6" t="n">
         <v>-0.1356</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-1.307819513860196</v>
       </c>
     </row>
@@ -546,9 +566,12 @@
         <v>35.79</v>
       </c>
       <c r="D7" t="n">
+        <v>1999</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.1947</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1.867622460071821</v>
       </c>
     </row>
@@ -563,9 +586,12 @@
         <v>37.602</v>
       </c>
       <c r="D8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.0506</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.4822722074420791</v>
       </c>
     </row>
@@ -580,9 +606,12 @@
         <v>35.578</v>
       </c>
       <c r="D9" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E9" t="n">
         <v>-0.0538</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-0.5214097243729454</v>
       </c>
     </row>
@@ -597,9 +626,12 @@
         <v>30.041</v>
       </c>
       <c r="D10" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E10" t="n">
         <v>-0.1556</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-1.500095746008668</v>
       </c>
     </row>
@@ -614,9 +646,12 @@
         <v>25.672</v>
       </c>
       <c r="D11" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E11" t="n">
         <v>-0.1454</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-1.402034867612948</v>
       </c>
     </row>
@@ -631,9 +666,12 @@
         <v>22.415</v>
       </c>
       <c r="D12" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E12" t="n">
         <v>-0.1269</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-1.224179352875611</v>
       </c>
     </row>
@@ -648,9 +686,12 @@
         <v>24.534</v>
       </c>
       <c r="D13" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.0945</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.9043185370079754</v>
       </c>
     </row>
@@ -665,9 +706,12 @@
         <v>20.82</v>
       </c>
       <c r="D14" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E14" t="n">
         <v>-0.1514</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>-1.459717737257489</v>
       </c>
     </row>
@@ -682,9 +726,12 @@
         <v>18.168</v>
       </c>
       <c r="D15" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E15" t="n">
         <v>-0.1274</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-1.228986258679323</v>
       </c>
     </row>
@@ -699,9 +746,12 @@
         <v>19.114</v>
       </c>
       <c r="D16" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.0521</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>0.4966929248532145</v>
       </c>
     </row>
@@ -716,9 +766,12 @@
         <v>18.377</v>
       </c>
       <c r="D17" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E17" t="n">
         <v>-0.0386</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>-0.3752797879401066</v>
       </c>
     </row>
@@ -733,9 +786,12 @@
         <v>18.668</v>
       </c>
       <c r="D18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.0158</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>0.1477115635037376</v>
       </c>
     </row>
@@ -750,9 +806,12 @@
         <v>19.732</v>
       </c>
       <c r="D19" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.057</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.5438006017295902</v>
       </c>
     </row>
@@ -767,9 +826,12 @@
         <v>18.985</v>
       </c>
       <c r="D20" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E20" t="n">
         <v>-0.0379</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>-0.3685501198149101</v>
       </c>
     </row>
@@ -784,9 +846,12 @@
         <v>19.866</v>
       </c>
       <c r="D21" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.0464</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.4418941986908999</v>
       </c>
     </row>
@@ -801,9 +866,12 @@
         <v>22.832</v>
       </c>
       <c r="D22" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.1493</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>1.431155413094789</v>
       </c>
     </row>
@@ -818,9 +886,12 @@
         <v>24.861</v>
       </c>
       <c r="D23" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.08890000000000001</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>0.8504811920064033</v>
       </c>
     </row>
@@ -835,9 +906,12 @@
         <v>25.648</v>
       </c>
       <c r="D24" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.0317</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>0.3005711680617729</v>
       </c>
     </row>
@@ -852,9 +926,12 @@
         <v>21.278</v>
       </c>
       <c r="D25" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E25" t="n">
         <v>-0.1704</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-1.642380157798538</v>
       </c>
     </row>
@@ -869,9 +946,12 @@
         <v>22.415</v>
       </c>
       <c r="D26" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.0534</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>0.5091908799428653</v>
       </c>
     </row>
@@ -886,9 +966,12 @@
         <v>22.662</v>
       </c>
       <c r="D27" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.011</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>0.1015652677881042</v>
       </c>
     </row>
@@ -903,9 +986,12 @@
         <v>21.447</v>
       </c>
       <c r="D28" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E28" t="n">
         <v>-0.0536</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>-0.5194869620514607</v>
       </c>
     </row>
@@ -920,9 +1006,12 @@
         <v>21.849</v>
       </c>
       <c r="D29" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E29" t="n">
         <v>0.0187</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>0.175591617165266</v>
       </c>
     </row>
@@ -937,9 +1026,12 @@
         <v>22.554</v>
       </c>
       <c r="D30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.0323</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>0.3063394550262271</v>
       </c>
     </row>
@@ -954,9 +1046,12 @@
         <v>22.352</v>
       </c>
       <c r="D31" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E31" t="n">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>-0.09071096436036787</v>
       </c>
     </row>
@@ -971,9 +1066,12 @@
         <v>24.324</v>
       </c>
       <c r="D32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E32" t="n">
         <v>0.0882</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>0.8437515238812067</v>
       </c>
     </row>
@@ -988,9 +1086,12 @@
         <v>23.975</v>
       </c>
       <c r="D33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E33" t="n">
         <v>-0.0143</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>-0.141664165879713</v>
       </c>
     </row>

--- a/data/exchange_rates/USD_CZK.xlsx
+++ b/data/exchange_rates/USD_CZK.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,13 +464,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>34337</v>
+        <v>33970</v>
       </c>
       <c r="C2" t="n">
-        <v>27.93</v>
+        <v>30.01</v>
       </c>
       <c r="D2" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -480,19 +480,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>34701</v>
+        <v>34337</v>
       </c>
       <c r="C3" t="n">
-        <v>26.661</v>
+        <v>27.93</v>
       </c>
       <c r="D3" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0454</v>
+        <v>-0.0693</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4406537068705871</v>
+        <v>-0.6552793497587301</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>35066</v>
+        <v>34701</v>
       </c>
       <c r="C4" t="n">
-        <v>27.213</v>
+        <v>26.661</v>
       </c>
       <c r="D4" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0207</v>
+        <v>-0.0454</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1948192403801133</v>
+        <v>-0.4234551076015108</v>
       </c>
     </row>
     <row r="5">
@@ -520,19 +520,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>35432</v>
+        <v>35066</v>
       </c>
       <c r="C5" t="n">
-        <v>34.657</v>
+        <v>27.213</v>
       </c>
       <c r="D5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2735</v>
+        <v>0.0207</v>
       </c>
       <c r="F5" t="n">
-        <v>2.625190814736801</v>
+        <v>0.217698967988121</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +540,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>35797</v>
+        <v>35432</v>
       </c>
       <c r="C6" t="n">
-        <v>29.957</v>
+        <v>34.657</v>
       </c>
       <c r="D6" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1356</v>
+        <v>0.2735</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.307819513860196</v>
+        <v>2.669798064948165</v>
       </c>
     </row>
     <row r="7">
@@ -560,19 +560,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>36164</v>
+        <v>35797</v>
       </c>
       <c r="C7" t="n">
-        <v>35.79</v>
+        <v>29.957</v>
       </c>
       <c r="D7" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1947</v>
+        <v>-0.1356</v>
       </c>
       <c r="F7" t="n">
-        <v>1.867622460071821</v>
+        <v>-1.298373377165577</v>
       </c>
     </row>
     <row r="8">
@@ -580,19 +580,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>36528</v>
+        <v>36164</v>
       </c>
       <c r="C8" t="n">
-        <v>37.602</v>
+        <v>35.79</v>
       </c>
       <c r="D8" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0506</v>
+        <v>0.1947</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4822722074420791</v>
+        <v>1.905457048965367</v>
       </c>
     </row>
     <row r="9">
@@ -600,19 +600,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>36893</v>
+        <v>36528</v>
       </c>
       <c r="C9" t="n">
-        <v>35.578</v>
+        <v>37.602</v>
       </c>
       <c r="D9" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0538</v>
+        <v>0.0506</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5214097243729454</v>
+        <v>0.5077217646617971</v>
       </c>
     </row>
     <row r="10">
@@ -620,19 +620,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>37258</v>
+        <v>36893</v>
       </c>
       <c r="C10" t="n">
-        <v>30.041</v>
+        <v>35.578</v>
       </c>
       <c r="D10" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1556</v>
+        <v>-0.0538</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.500095746008668</v>
+        <v>-0.5049330839245502</v>
       </c>
     </row>
     <row r="11">
@@ -640,19 +640,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>37622</v>
+        <v>37258</v>
       </c>
       <c r="C11" t="n">
-        <v>25.672</v>
+        <v>30.041</v>
       </c>
       <c r="D11" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1454</v>
+        <v>-0.1556</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.402034867612948</v>
+        <v>-1.4923685588871</v>
       </c>
     </row>
     <row r="12">
@@ -660,19 +660,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>37987</v>
+        <v>37622</v>
       </c>
       <c r="C12" t="n">
-        <v>22.415</v>
+        <v>25.672</v>
       </c>
       <c r="D12" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1269</v>
+        <v>-0.1454</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.224179352875611</v>
+        <v>-1.393431016209123</v>
       </c>
     </row>
     <row r="13">
@@ -680,19 +680,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>38355</v>
+        <v>37987</v>
       </c>
       <c r="C13" t="n">
-        <v>24.534</v>
+        <v>22.415</v>
       </c>
       <c r="D13" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0945</v>
+        <v>-0.1269</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9043185370079754</v>
+        <v>-1.213985473116715</v>
       </c>
     </row>
     <row r="14">
@@ -700,19 +700,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>38719</v>
+        <v>38355</v>
       </c>
       <c r="C14" t="n">
-        <v>20.82</v>
+        <v>24.534</v>
       </c>
       <c r="D14" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1514</v>
+        <v>0.0945</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.459717737257489</v>
+        <v>0.9335411885405389</v>
       </c>
     </row>
     <row r="15">
@@ -720,19 +720,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>39083</v>
+        <v>38719</v>
       </c>
       <c r="C15" t="n">
-        <v>18.168</v>
+        <v>20.82</v>
       </c>
       <c r="D15" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1274</v>
+        <v>-0.1514</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.228986258679323</v>
+        <v>-1.45162957072558</v>
       </c>
     </row>
     <row r="16">
@@ -740,19 +740,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>39448</v>
+        <v>39083</v>
       </c>
       <c r="C16" t="n">
-        <v>19.114</v>
+        <v>18.168</v>
       </c>
       <c r="D16" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0521</v>
+        <v>-0.1274</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4966929248532145</v>
+        <v>-1.218835352659753</v>
       </c>
     </row>
     <row r="17">
@@ -760,19 +760,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>39814</v>
+        <v>39448</v>
       </c>
       <c r="C17" t="n">
-        <v>18.377</v>
+        <v>19.114</v>
       </c>
       <c r="D17" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0386</v>
+        <v>0.0521</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3752797879401066</v>
+        <v>0.5222714032909113</v>
       </c>
     </row>
     <row r="18">
@@ -780,19 +780,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>40179</v>
+        <v>39814</v>
       </c>
       <c r="C18" t="n">
-        <v>18.668</v>
+        <v>18.377</v>
       </c>
       <c r="D18" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0158</v>
+        <v>-0.0386</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1477115635037376</v>
+        <v>-0.3574967458161931</v>
       </c>
     </row>
     <row r="19">
@@ -800,19 +800,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>40546</v>
+        <v>40179</v>
       </c>
       <c r="C19" t="n">
-        <v>19.732</v>
+        <v>18.668</v>
       </c>
       <c r="D19" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E19" t="n">
-        <v>0.057</v>
+        <v>0.0158</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5438006017295902</v>
+        <v>0.170170148466348</v>
       </c>
     </row>
     <row r="20">
@@ -820,19 +820,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>40910</v>
+        <v>40546</v>
       </c>
       <c r="C20" t="n">
-        <v>18.985</v>
+        <v>19.732</v>
       </c>
       <c r="D20" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0379</v>
+        <v>0.057</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3685501198149101</v>
+        <v>0.5698002228126843</v>
       </c>
     </row>
     <row r="21">
@@ -840,19 +840,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>41275</v>
+        <v>40910</v>
       </c>
       <c r="C21" t="n">
-        <v>19.866</v>
+        <v>18.985</v>
       </c>
       <c r="D21" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0464</v>
+        <v>-0.0379</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4418941986908999</v>
+        <v>-0.3507069144559399</v>
       </c>
     </row>
     <row r="22">
@@ -860,19 +860,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>41640</v>
+        <v>41275</v>
       </c>
       <c r="C22" t="n">
-        <v>22.832</v>
+        <v>19.866</v>
       </c>
       <c r="D22" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1493</v>
+        <v>0.0464</v>
       </c>
       <c r="F22" t="n">
-        <v>1.431155413094789</v>
+        <v>0.4669827765002774</v>
       </c>
     </row>
     <row r="23">
@@ -880,19 +880,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>42005</v>
+        <v>41640</v>
       </c>
       <c r="C23" t="n">
-        <v>24.861</v>
+        <v>22.832</v>
       </c>
       <c r="D23" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1493</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8504811920064033</v>
+        <v>1.46508798645751</v>
       </c>
     </row>
     <row r="24">
@@ -900,19 +900,19 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>42370</v>
+        <v>42005</v>
       </c>
       <c r="C24" t="n">
-        <v>25.648</v>
+        <v>24.861</v>
       </c>
       <c r="D24" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0317</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3005711680617729</v>
+        <v>0.8792225376585127</v>
       </c>
     </row>
     <row r="25">
@@ -920,19 +920,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>42737</v>
+        <v>42370</v>
       </c>
       <c r="C25" t="n">
-        <v>21.278</v>
+        <v>25.648</v>
       </c>
       <c r="D25" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1704</v>
+        <v>0.0317</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.642380157798538</v>
+        <v>0.3243963179349584</v>
       </c>
     </row>
     <row r="26">
@@ -940,19 +940,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>43101</v>
+        <v>42737</v>
       </c>
       <c r="C26" t="n">
-        <v>22.415</v>
+        <v>21.278</v>
       </c>
       <c r="D26" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0534</v>
+        <v>-0.1704</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5091908799428653</v>
+        <v>-1.635924993361026</v>
       </c>
     </row>
     <row r="27">
@@ -960,19 +960,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>43466</v>
+        <v>43101</v>
       </c>
       <c r="C27" t="n">
-        <v>22.662</v>
+        <v>22.415</v>
       </c>
       <c r="D27" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E27" t="n">
-        <v>0.011</v>
+        <v>0.0534</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1015652677881042</v>
+        <v>0.5348810901028103</v>
       </c>
     </row>
     <row r="28">
@@ -980,19 +980,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="C28" t="n">
-        <v>21.447</v>
+        <v>22.662</v>
       </c>
       <c r="D28" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0536</v>
+        <v>0.011</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5194869620514607</v>
+        <v>0.1236113048531826</v>
       </c>
     </row>
     <row r="29">
@@ -1000,19 +1000,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>44197</v>
+        <v>43831</v>
       </c>
       <c r="C29" t="n">
-        <v>21.849</v>
+        <v>21.447</v>
       </c>
       <c r="D29" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0187</v>
+        <v>-0.0536</v>
       </c>
       <c r="F29" t="n">
-        <v>0.175591617165266</v>
+        <v>-0.502993132107335</v>
       </c>
     </row>
     <row r="30">
@@ -1020,19 +1020,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>44564</v>
+        <v>44197</v>
       </c>
       <c r="C30" t="n">
-        <v>22.554</v>
+        <v>21.849</v>
       </c>
       <c r="D30" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0323</v>
+        <v>0.0187</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3063394550262271</v>
+        <v>0.1982994498159688</v>
       </c>
     </row>
     <row r="31">
@@ -1040,19 +1040,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>44928</v>
+        <v>44564</v>
       </c>
       <c r="C31" t="n">
-        <v>22.352</v>
+        <v>22.554</v>
       </c>
       <c r="D31" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.09071096436036787</v>
+        <v>0.3302161733866041</v>
       </c>
     </row>
     <row r="32">
@@ -1060,19 +1060,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45292</v>
+        <v>44928</v>
       </c>
       <c r="C32" t="n">
-        <v>24.324</v>
+        <v>22.352</v>
       </c>
       <c r="D32" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0882</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8437515238812067</v>
+        <v>-0.07038387686833987</v>
       </c>
     </row>
     <row r="33">
@@ -1080,19 +1080,39 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C33" t="n">
+        <v>24.324</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.8724327062982594</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C34" t="n">
         <v>23.975</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D34" t="n">
         <v>2025</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E34" t="n">
         <v>-0.0143</v>
       </c>
-      <c r="F33" t="n">
-        <v>-0.141664165879713</v>
+      <c r="F34" t="n">
+        <v>-0.1217926000245433</v>
       </c>
     </row>
   </sheetData>

--- a/data/exchange_rates/USD_CZK.xlsx
+++ b/data/exchange_rates/USD_CZK.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Returns</t>
+          <t>Log_return</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -489,10 +489,10 @@
         <v>1994</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0693</v>
+        <v>-0.0718</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6552793497587301</v>
+        <v>-0.6317344371125823</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         <v>1995</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0454</v>
+        <v>-0.0465</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4234551076015108</v>
+        <v>-0.3850374468143252</v>
       </c>
     </row>
     <row r="5">
@@ -529,10 +529,10 @@
         <v>1996</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0207</v>
+        <v>0.0205</v>
       </c>
       <c r="F5" t="n">
-        <v>0.217698967988121</v>
+        <v>0.2682707883628774</v>
       </c>
     </row>
     <row r="6">
@@ -549,10 +549,10 @@
         <v>1997</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2735</v>
+        <v>0.2418</v>
       </c>
       <c r="F6" t="n">
-        <v>2.669798064948165</v>
+        <v>2.426138138283996</v>
       </c>
     </row>
     <row r="7">
@@ -569,10 +569,10 @@
         <v>1998</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1356</v>
+        <v>-0.1457</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.298373377165577</v>
+        <v>-1.352323669643855</v>
       </c>
     </row>
     <row r="8">
@@ -589,10 +589,10 @@
         <v>1999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1947</v>
+        <v>0.1779</v>
       </c>
       <c r="F8" t="n">
-        <v>1.905457048965367</v>
+        <v>1.803057597570216</v>
       </c>
     </row>
     <row r="9">
@@ -609,10 +609,10 @@
         <v>2000</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0506</v>
+        <v>0.0494</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5077217646617971</v>
+        <v>0.5500709077154319</v>
       </c>
     </row>
     <row r="10">
@@ -629,10 +629,10 @@
         <v>2001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0538</v>
+        <v>-0.0553</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5049330839245502</v>
+        <v>-0.470845095613719</v>
       </c>
     </row>
     <row r="11">
@@ -649,10 +649,10 @@
         <v>2002</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1556</v>
+        <v>-0.1692</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4923685588871</v>
+        <v>-1.581469095414963</v>
       </c>
     </row>
     <row r="12">
@@ -669,10 +669,10 @@
         <v>2003</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1454</v>
+        <v>-0.1572</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.393431016209123</v>
+        <v>-1.464458665233972</v>
       </c>
     </row>
     <row r="13">
@@ -689,10 +689,10 @@
         <v>2004</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1269</v>
+        <v>-0.1357</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.213985473116715</v>
+        <v>-1.254814977826362</v>
       </c>
     </row>
     <row r="14">
@@ -709,10 +709,10 @@
         <v>2005</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0945</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9335411885405389</v>
+        <v>0.9488814572489781</v>
       </c>
     </row>
     <row r="15">
@@ -729,10 +729,10 @@
         <v>2006</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1514</v>
+        <v>-0.1641</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.45162957072558</v>
+        <v>-1.531739662588042</v>
       </c>
     </row>
     <row r="16">
@@ -749,10 +749,10 @@
         <v>2007</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1274</v>
+        <v>-0.1363</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.218835352659753</v>
+        <v>-1.260665499335412</v>
       </c>
     </row>
     <row r="17">
@@ -769,10 +769,10 @@
         <v>2008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0521</v>
+        <v>0.0508</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5222714032909113</v>
+        <v>0.5637221245698809</v>
       </c>
     </row>
     <row r="18">
@@ -789,10 +789,10 @@
         <v>2009</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0386</v>
+        <v>-0.0393</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3574967458161931</v>
+        <v>-0.3148311887057303</v>
       </c>
     </row>
     <row r="19">
@@ -809,10 +809,10 @@
         <v>2010</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0158</v>
+        <v>0.0157</v>
       </c>
       <c r="F19" t="n">
-        <v>0.170170148466348</v>
+        <v>0.2214666162904808</v>
       </c>
     </row>
     <row r="20">
@@ -829,10 +829,10 @@
         <v>2011</v>
       </c>
       <c r="E20" t="n">
-        <v>0.057</v>
+        <v>0.0554</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5698002228126843</v>
+        <v>0.6085761228059277</v>
       </c>
     </row>
     <row r="21">
@@ -849,10 +849,10 @@
         <v>2012</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0379</v>
+        <v>-0.0386</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3507069144559399</v>
+        <v>-0.3080055802785058</v>
       </c>
     </row>
     <row r="22">
@@ -869,10 +869,10 @@
         <v>2013</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0464</v>
+        <v>0.0454</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4669827765002774</v>
+        <v>0.5110674309884348</v>
       </c>
     </row>
     <row r="23">
@@ -889,10 +889,10 @@
         <v>2014</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1493</v>
+        <v>0.1392</v>
       </c>
       <c r="F23" t="n">
-        <v>1.46508798645751</v>
+        <v>1.425698960236518</v>
       </c>
     </row>
     <row r="24">
@@ -909,10 +909,10 @@
         <v>2015</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0851</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8792225376585127</v>
+        <v>0.8981769375038817</v>
       </c>
     </row>
     <row r="25">
@@ -929,10 +929,10 @@
         <v>2016</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0317</v>
+        <v>0.0312</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3243963179349584</v>
+        <v>0.3726050886075948</v>
       </c>
     </row>
     <row r="26">
@@ -949,10 +949,10 @@
         <v>2017</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1704</v>
+        <v>-0.1868</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.635924993361026</v>
+        <v>-1.753084393013751</v>
       </c>
     </row>
     <row r="27">
@@ -969,10 +969,10 @@
         <v>2018</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0534</v>
+        <v>0.0521</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5348810901028103</v>
+        <v>0.576398254506155</v>
       </c>
     </row>
     <row r="28">
@@ -992,7 +992,7 @@
         <v>0.011</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1236113048531826</v>
+        <v>0.1756375311362591</v>
       </c>
     </row>
     <row r="29">
@@ -1009,10 +1009,10 @@
         <v>2020</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0536</v>
+        <v>-0.0551</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.502993132107335</v>
+        <v>-0.4688949217773691</v>
       </c>
     </row>
     <row r="30">
@@ -1029,10 +1029,10 @@
         <v>2021</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0187</v>
+        <v>0.0186</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1982994498159688</v>
+        <v>0.2497441369175537</v>
       </c>
     </row>
     <row r="31">
@@ -1049,10 +1049,10 @@
         <v>2022</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0323</v>
+        <v>0.0318</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3302161733866041</v>
+        <v>0.3784556101166444</v>
       </c>
     </row>
     <row r="32">
@@ -1072,7 +1072,7 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.07038387686833987</v>
+        <v>-0.01937985249872672</v>
       </c>
     </row>
     <row r="33">
@@ -1089,10 +1089,10 @@
         <v>2024</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0882</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8724327062982594</v>
+        <v>0.8923264159948322</v>
       </c>
     </row>
     <row r="34">
@@ -1109,10 +1109,10 @@
         <v>2025</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0143</v>
+        <v>-0.0145</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1217926000245433</v>
+        <v>-0.07300963299834784</v>
       </c>
     </row>
   </sheetData>
